--- a/docs/test-report/cve-2026-109618-109619-coverage-matrix-2026-10-24.xlsx
+++ b/docs/test-report/cve-2026-109618-109619-coverage-matrix-2026-10-24.xlsx
@@ -3055,9 +3055,9 @@
           <t>Across 55 directories</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
@@ -3181,9 +3181,9 @@
           <t>Always authoritative; other copies are build-context mirrors</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
     </row>
